--- a/example_output/spreadsheets/indirect_costs_initial.xlsx
+++ b/example_output/spreadsheets/indirect_costs_initial.xlsx
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202001</v>
+        <v>202401</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202002</v>
+        <v>202402</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202003</v>
+        <v>202403</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202004</v>
+        <v>202404</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202005</v>
+        <v>202405</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202006</v>
+        <v>202406</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>

--- a/example_output/spreadsheets/indirect_costs_initial.xlsx
+++ b/example_output/spreadsheets/indirect_costs_initial.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202401</v>
+        <v>202301</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202402</v>
+        <v>202302</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202403</v>
+        <v>202303</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202404</v>
+        <v>202304</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202405</v>
+        <v>202305</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202406</v>
+        <v>202306</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
